--- a/LubanLaunchConfig/Datas/LaunchPreConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchPreConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_MagicWealth\ClientConfig\LubanLaunchConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\gt_jogosup777\ClientConfig\LubanLaunchConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -125,15 +125,15 @@
     <t>English</t>
   </si>
   <si>
-    <t>MagicWealthTestRes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>(list#sep=;),string</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>JogosUpTestRes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -644,7 +644,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>15</v>
@@ -723,10 +723,10 @@
         <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>28</v>

--- a/LubanLaunchConfig/Datas/LaunchPreConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchPreConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_MagicWealth\ClientConfig\LubanLaunchConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\DoubleJackpotClub\ClientConfig\LubanLaunchConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -125,15 +125,15 @@
     <t>English</t>
   </si>
   <si>
-    <t>MagicWealthTestRes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>(list#sep=;),string</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>DoubleJackpotClubTestRes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -644,7 +644,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>15</v>
@@ -723,10 +723,10 @@
         <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>28</v>

--- a/LubanLaunchConfig/Datas/LaunchPreConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchPreConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_MagicWealth\ClientConfig\LubanLaunchConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_CandyVegas\ClientConfig\LubanLaunchConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -125,15 +125,15 @@
     <t>English</t>
   </si>
   <si>
-    <t>MagicWealthTestRes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>(list#sep=;),string</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <t>https://awsgamesres.s3.amazonaws.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CandyVegasRes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -644,7 +644,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>15</v>
@@ -723,10 +723,10 @@
         <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>28</v>

--- a/LubanLaunchConfig/Datas/LaunchPreConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchPreConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_MagicWealth\ClientConfig\LubanLaunchConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\games_Luckybillionspin_10\ClientConfig\LubanLaunchConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -125,15 +125,15 @@
     <t>English</t>
   </si>
   <si>
-    <t>MagicWealthTestRes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>(list#sep=;),string</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>GTLuckyBillionSpinhTestRes</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -644,7 +644,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>15</v>
@@ -723,10 +723,10 @@
         <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>34</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>28</v>

--- a/LubanLaunchConfig/Datas/LaunchPreConfig.xlsx
+++ b/LubanLaunchConfig/Datas/LaunchPreConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\game_MagicWealth\ClientConfig\LubanLaunchConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitClient\games_bigwinroyale\ClientConfig\LubanLaunchConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -125,15 +125,15 @@
     <t>English</t>
   </si>
   <si>
-    <t>MagicWealthTestRes</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>(list#sep=;),string</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>https://gamesgt.s3.ap-southeast-1.amazonaws.com</t>
+    <t>BigWinRoyalehTestRes</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://slotapp.s3.amazonaws.com/resource</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -644,7 +644,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>15</v>
@@ -726,7 +726,7 @@
         <v>36</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>28</v>
